--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -488,11 +488,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>коэффициент обеспеченности собственными оборотными средствами 2023 401 9 846 2 40 7 111 1 704 2 14 6</t>
+          <t>коэффициент обеспеченности собственными оборотными средствами 2023</t>
         </is>
       </c>
     </row>
@@ -526,51 +526,51 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>коэффициент обеспеченности собственными оборотными средствами 2023 35 6 28 9 50 9 98 8 96 9 81 8 29 4 59 0 72 4 62 4 49 2 68 9 7 2</t>
+          <t>коэффициент обеспеченности собственными оборотными средствами 2023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>от переподажи финансовых вложений</t>
+          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) прочие расходы</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtPereprodFinVlozh</t>
+          <t>OtcGo(raSalProDohIRasProRas</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>в том числе от продажи внеоборотных активов кроме финансовых вложений 14 403 27 862</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -579,32 +579,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) прочие расходы</t>
+          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) прочие доходы</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProRas</t>
+          <t>OtcGo(raSalProDohIRasProDoh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов 26 192 421 24 539 666 16 212 8 936 1 515 800 669 10</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -613,32 +613,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) прочие доходы</t>
+          <t>отчетный год отложенный налог на прибыль</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProDoh</t>
+          <t>OtcGoOtlNalNaPri_1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов 26 192 421 24 539 666 16 212 8 936 1 515 800 669 10</t>
+          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -647,66 +647,66 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) доходы от участия в других организациях</t>
+          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) проценты к уплате</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasDohOtUchVDruOrg</t>
+          <t>OtcGo(raSalProDohIRasProKUpl</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов 26 192 421 24 539 666 16 212 8 936 1 515 800 669 10</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t29Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) проценты к получению</t>
+          <t>от переподажи финансовых вложений</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProKPol</t>
+          <t>OtPereprodFinVlozh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов 26 192 421 24 539 666 16 212 8 936 1 515 800 669 10</t>
+          <t>в том числе от продажи внеоборотных активов кроме финансовых вложений</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -715,32 +715,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) проценты к уплате</t>
+          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) проценты к получению</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProKUpl</t>
+          <t>OtcGo(raSalProDohIRasProKPol</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов 26 192 421 24 539 666 16 212 8 936 1 515 800 669 10</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -749,32 +749,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>отчетный год отложенный налог на прибыль</t>
+          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) доходы от участия в других организациях</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri_1</t>
+          <t>OtcGo(raSalProDohIRasDohOtUchVDruOrg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль 3 476 083 3 675 830 4 840 128 197 30 755 13 338 29 046 19 468 35 5</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -783,66 +783,66 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>отчетный год налог на прибыль от операций, результат которых не включается в чистую прибыль (убыток) периода</t>
+          <t>отчетный год уровень коммерческих и управленческих расходов к валовой прибыли</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OtcGoNalNaPriOtOpeRezKotNeVklVChiPri(ubPer</t>
+          <t>OtcGoUroKomIUprRasKValPri</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.36</v>
+        <v>0.55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль 3 476 083 3 675 830 4 840 128 197 30 755 13 338 29 046 19 468 35 5</t>
+          <t>коммерческие и управленческие расходы коммерческие и управленческие расходы</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>отчетный год текущий налог на прибыль</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal</t>
+          <t>OtcGoTekNalNaPri_1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.35</v>
+        <v>0.54</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>валюта баланса 2023 1 142 1 142 236 236 656 629 639 388 17 241</t>
+          <t>текущий налог на прибыль текущий налог на прибыль текущий налог на прибыль</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -851,100 +851,100 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>отчетный год текущий налог на прибыль</t>
+          <t>отчетный год сальдо прочих доходов и расходов</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OtcGoTekNalNaPri_1</t>
+          <t>OtcGoSalProDohIRas_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль текущий налог на прибыль текущий налог на прибыль 4 371 599 3 277 816 1 050 8 472 689 258 348 80 221 236 978 1 390 251 259</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>отчетный год прибыль (убыток) до налогообложения</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg</t>
+          <t>OtcGoPri(ubDoNal_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>валюта баланса 2023 1 142 1 142 236 236 656 629 639 388 17 241</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T24_000000_t13Ved14.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>отчетный год прочее</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>OtcGoPro_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>запасы длительность 1 оборота 0 0 0 0 0 0 0 0 53 6 600 4 1 5</t>
+          <t>прочее прочее прочее</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -953,32 +953,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>отчетный год сальдо прочих доходов и расходов</t>
+          <t>отчетный год чистая прибыль (убыток) отчетного периода</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OtcGoSalProDohIRas_1</t>
+          <t>OtcGoChiPri(ubOtcPer_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов 26 192 421 24 539 666 16 212 8 936 1 515 800 669 10</t>
+          <t>на конец года тысяч рублей прибыль убыток от продаж прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -987,80 +987,80 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>отчетный год уровень коммерческих и управленческих расходов к валовой прибыли</t>
+          <t>отчетный год налог на прибыль от операций, результат которых не включается в чистую прибыль (убыток) периода</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OtcGoUroKomIUprRasKValPri</t>
+          <t>OtcGoNalNaPriOtOpeRezKotNeVklVChiPri(ubPer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">коммерческие и управленческие расходы коммерческие и управленческие расходы 50 117 067 34 775 932 59 731 12 931 2 008 4 451 768 1 899 638 1 619 509 3 </t>
+          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>отчетный год прибыль (убыток) до налогообложения</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OtcGoPri(ubDoNal_1</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль 3 476 083 3 675 830 4 840 128 197 30 755 13 338 29 046 19 468 35 5</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t01Ved14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>отчетный год чистая прибыль (убыток) отчетного периода</t>
+          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OtcGoChiPri(ubOtcPer_1</t>
+          <t>ValBalUbyOrgNaKonGoV%KValBal</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1070,31 +1070,31 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль 3 476 083 3 675 830 4 840 128 197 30 755 13 338 29 046 19 468 35 5</t>
+          <t>валюта баланса 2023 валюта баланса 2023 валюта баланса 2023 валюта баланса 2023</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t01Ved14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>отчетный год прочее</t>
+          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OtcGoPro_1</t>
+          <t>ValBalUbyOrgNaKonGoItAktUbyOrg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1104,17 +1104,17 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>продолжение таблицы 12</t>
+          <t>валюта баланса 2023 валюта баланса 2023 валюта баланса 2023 валюта баланса 2023</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1123,32 +1123,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>отчетный год совокупный финансовый результат периода</t>
+          <t>отчетный год результат от прочих операций, не включаемых в чистую прибыль (убыток) периода</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OtcGoSovFinRezPer_1</t>
+          <t>OtcGoRezOtProOpeNeVklVChiPri(ubPer_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль 3 476 083 3 675 830 4 840 128 197 30 755 13 338 29 046 19 468 35 5</t>
+          <t>на конец года тысяч рублей прибыль убыток от продаж прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1157,32 +1157,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>отчетный год результат от прочих операций, не включаемых в чистую прибыль (убыток) периода</t>
+          <t>отчетный год совокупный финансовый результат периода</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OtcGoRezOtProOpeNeVklVChiPri(ubPer_1</t>
+          <t>OtcGoSovFinRezPer_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль текущий налог на прибыль текущий налог на прибыль 4 371 599 3 277 816 1 050 8 472 689 258 348 80 221 236 978 1 390 251 259</t>
+          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1191,94 +1191,94 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
+          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>валюта баланса 2023 731 078 261 510 134 382 473 989 147 908 3 826 98 918 91 189 798 59 137 171 25 203 480 44 161 896 7 803 414 40 126 683 821 732</t>
+          <t>на конец года тысяч рублей оборотные активы 2023</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>T24_000000_t01Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>отчетный год результат от переоценки внеоборотных активов, не включаемых в чистую прибыль (убыток) периода</t>
+          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OtcGoRezOtPerVneAktNeVklVChiPri(ubPer_1</t>
+          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль 3 476 083 3 675 830 4 840 128 197 30 755 13 338 29 046 19 468 35 5</t>
+          <t>на конец года тысяч рублей оборотные активы 2023</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14mo8.xlsx</t>
+          <t>T24_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>отчетный год результат от переоценки внеоборотных активов, не включаемых в чистую прибыль (убыток) периода</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
+          <t>OtcGoRezOtPerVneAktNeVklVChiPri(ubPer_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>валюта баланса 2023 731 078 261 510 134 382 473 989 147 908 3 826 98 918 91 189 798 59 137 171 25 203 480 44 161 896 7 803 414 40 126 683 821 732</t>
+          <t>на конец года тысяч рублей прибыль убыток от продаж прибыль убыток от продаж</t>
         </is>
       </c>
     </row>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,825 +460,2337 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T24_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>коэффициент обеспеченности собственными материальными оборотными средствами</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: долгосрочным обязательствам</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KoeObeSobMatOboSre</t>
+          <t>ChiPriUby(-DoNalV%K:DolOby</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>коэффициент обеспеченности собственными оборотными средствами 2023</t>
+          <t>прибыль убыток до налогообложения в к долгосрочным обязательствам</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T24_000000_t22Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>коэффициент обеспеченности собственными материальными оборотными средствами</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: краткосрочным обязательствам</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KoeObeSobMatOboSre_1</t>
+          <t>ChiPriUby(-DoNalV%K:KraOby</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>коэффициент обеспеченности собственными оборотными средствами 2023</t>
+          <t>прибыль убыток до налогообложения в к краткосрочным обязательствам</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) прочие расходы</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: долгосрочным обязательствам</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProRas</t>
+          <t>ChiPriUby(-DoNalV%K:DolOby_1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>0.95</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения в к долгосрочным обязательствам</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) прочие доходы</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: краткосрочным обязательствам</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProDoh</t>
+          <t>ChiPriUby(-DoNalV%K:KraOby_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения в к краткосрочным обязательствам</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>отчетный год отложенный налог на прибыль</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: внеоборотным активам</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtcGoOtlNalNaPri_1</t>
+          <t>ChiPriUby(-DoNalV%K:VneAkt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль</t>
+          <t>прибыль убыток до налогообложения в к внеоборотным активам</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) проценты к уплате</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: оборотным активам</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProKUpl</t>
+          <t>ChiPriUby(-DoNalV%K:OboAkt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения в к оборотным активам</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T24_000000_t29Ved14.xlsx</t>
+          <t>M25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>от переподажи финансовых вложений</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: капиталу и резервам</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OtPereprodFinVlozh</t>
+          <t>ChiPriUby(-DoNalV%K:KapIRez</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>в том числе от продажи внеоборотных активов кроме финансовых вложений</t>
+          <t>прибыль убыток до налогообложения в к капиталу и резервам</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) проценты к получению</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: внеоборотным активам</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasProKPol</t>
+          <t>ChiPriUby(-DoNalV%K:VneAkt_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения в к внеоборотным активам</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>отчетный год (расшифровка сальдо прочих доходов и расходов) доходы от участия в других организациях</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: оборотным активам</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OtcGo(raSalProDohIRasDohOtUchVDruOrg</t>
+          <t>ChiPriUby(-DoNalV%K:OboAkt_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения в к оборотным активам</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>отчетный год уровень коммерческих и управленческих расходов к валовой прибыли</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: капиталу и резервам</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OtcGoUroKomIUprRasKValPri</t>
+          <t>ChiPriUby(-DoNalV%K:KapIRez_1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>коммерческие и управленческие расходы коммерческие и управленческие расходы</t>
+          <t>прибыль убыток до налогообложения в к капиталу и резервам</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>отчетный год текущий налог на прибыль</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: всем активам</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OtcGoTekNalNaPri_1</t>
+          <t>ChiPriUby(-DoNalV%K:VsAkt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.54</v>
+        <v>0.93</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>текущий налог на прибыль текущий налог на прибыль текущий налог на прибыль</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t27Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>отчетный год сальдо прочих доходов и расходов</t>
+          <t>чистая прибыль, убыток (-) до налогообложения в % к: всем активам</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OtcGoSalProDohIRas_1</t>
+          <t>ChiPriUby(-DoNalV%K:VsAkt_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.53</v>
+        <v>0.93</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения в к всем активам</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>отчетный год прибыль (убыток) до налогообложения</t>
+          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OtcGoPri(ubDoNal_1</t>
+          <t>OrgPolUbyOtProKolOrg(ed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.52</v>
+        <v>0.85</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>отчетный год прочее</t>
+          <t>организации, получившие убыток от продаж: в % к общему количеству организаций</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OtcGoPro_1</t>
+          <t>OrgPolUbyOtProV%KObsKolOrg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>прочее прочее прочее</t>
+          <t>организации получившие прибыль в к общему количеству</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>отчетный год чистая прибыль (убыток) отчетного периода</t>
+          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OtcGoChiPri(ubOtcPer_1</t>
+          <t>RenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов к себестоимости продаж с учетом коммерческ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>отчетный год налог на прибыль от операций, результат которых не включается в чистую прибыль (убыток) периода</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OtcGoNalNaPriOtOpeRezKotNeVklVChiPri(ubPer</t>
+          <t>PriUby(-DoNalZaPreGo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.49</v>
+        <v>0.68</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T24_000000_t13Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>PriUby(-DoNalZaPreGo_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>117</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal</t>
+          <t>PriUby(-DoNalZaPreGo_2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>валюта баланса 2023 валюта баланса 2023 валюта баланса 2023 валюта баланса 2023</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>рентабельность, убыточность (-) в % к выручке</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg</t>
+          <t>RenUby(-V%KVyr</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>валюта баланса 2023 валюта баланса 2023 валюта баланса 2023 валюта баланса 2023</t>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>отчетный год результат от прочих операций, не включаемых в чистую прибыль (убыток) периода</t>
+          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OtcGoRezOtProOpeNeVklVChiPri(ubPer_1</t>
+          <t>RenUby(-V%ChiPri(ubKVyr</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>тысяч рублей уровень рентабельности убыточности в чистой прибыли убытка к выручке чистой прибыли убытка к выручке</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>отчетный год совокупный финансовый результат периода</t>
+          <t>организации, получившие убыток от продаж: убыточность в % :</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OtcGoSovFinRezPer_1</t>
+          <t>OrgPolUbyOtProUbyV%:</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>отложенный налог на прибыль отложенный налог на прибыль отложенный налог на прибыль</t>
+          <t>организации получившие прибыль в к общему количеству</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16</v>
+        <v>132</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>организации, получившие убыток от продаж: убыток от продажи</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
+          <t>OrgPolUbyOtProUbyOtPro</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2023</t>
+          <t>продолжение таблицы 16 организации получившие убыток убыток 3 480</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T24_000000_t01Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2023</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>отчетный год результат от переоценки внеоборотных активов, не включаемых в чистую прибыль (убыток) периода</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OtcGoRezOtPerVneAktNeVklVChiPri(ubPer_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>количество организаций единиц количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>KolOrgPolUbyZaPreGo(ed_2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>количество организаций единиц количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>144</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>50</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M25_000000_t23FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>60</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>70</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов к себестоимости продаж с учетом коммерческ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>138</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RenUby(-V%KSebProSUchKomIUprRas_1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>долгосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DolOby_1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>внеоборотные активы 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>140</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RenUby(-V%ChiPri(ubKVyr_1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам чистая прибыль убыток в ко всем активам 3 8 5 1 8 8 6 8 10 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>88</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>темп роста прибыли (убытка) в %</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TeRosPri(ubV%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>103</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>темп роста прибыли (убытка) в %</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TeRosPri(ubV%_1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>темп роста прибыли (убытка) в %</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TeRosPri(ubV%_2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M25_000000_t13Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SreStoOboAktTys</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>оборотные активы длительность 1 оборота</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>краткосрочные обязательства</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>KraOby_1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>внеоборотные активы 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>соотношение собственных и заемных средств</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SooSobIZaeSre</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 9 обязательства без заемных средств 2025 61 291 796 15 128 217 45 150 92 736 37 600 55 136</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>44</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>доля источников финансирования (источники собственных средств и долгосрочные обязательства) в валюте баланса</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DolIstFin(isSobSreIDolObyVValBal</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>соотношение заемных и собственных средств нормальное ограничение меньше либо равно 100 2024 соотношение заемных и собственных средств нормальное огран</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ValBalUbyOrgNaKonGoItAktUbyOrg</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>на конец года тысяч рублей оборотные активы 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>на конец года тысяч рублей оборотные активы 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>91</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>сумма прибыли за предыдущий год</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SumPriZaPreGo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>организации получившие прибыль количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>92</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>темп роста убытка в %</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TeRosUbyV%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>106</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>сумма прибыли за предыдущий год</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SumPriZaPreGo_1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>организации получившие прибыль количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>107</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>темп роста убытка в %</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TeRosUbyV%_1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>сумма прибыли за предыдущий год</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SumPriZaPreGo_2</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>организации получившие прибыль количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>темп роста убытка в %</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TeRosUbyV%_2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ValBalUbyOrgNaKonGoV%KValBal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
         <v>0.34</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>на конец года тысяч рублей прибыль убыток от продаж прибыль убыток от продаж</t>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>на конец года тысяч рублей оборотные активы 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>на конец года тысяч рублей оборотные активы 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>139</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>рентабельность, убыточность (-) в % к выручке</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RenUby(-V%KVyr_1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>прибыль убыток до налогообложения в к всем активам 4 8 4 0 14 5 16 1 13 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>M25_000000_t22Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>коэффициент текущей ликвидности (покрытия) (нормальное ограничение 200 %)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>KoeTekLik(po(noOgr20%)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>соотношение заемных и собственных средств нормальное ограничение меньше либо равно 100 2024 соотношение заемных и собственных средств нормальное огран</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>89</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>сумма убытка за предыдущий год</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SumUbyZaPreGo</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>организации получившие убыток количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>104</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>сумма убытка за предыдущий год</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SumUbyZaPreGo_1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>организации получившие убыток количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>119</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>сумма убытка за предыдущий год</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SumUbyZaPreGo_2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>организации получившие убыток количество организаций единиц</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>93</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>темп роста суммы прибыли в %</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TeRosSumPriV%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>108</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>темп роста суммы прибыли в %</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TeRosSumPriV%_1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>темп роста суммы прибыли в %</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TeRosSumPriV%_2</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>тысяч рублей организации получившие убыток убыток</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>M25_000000_t01Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>капитал и резервы</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>KapIRez_1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>валюта баланса 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>M25_000000_t23FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>прочие расходы</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ProRas</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>68</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>прочие расходы</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ProRas_1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>78</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>прочие расходы</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ProRas_2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>M25_000000_t23FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>проценты к уплате</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ProKUpl</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 10 другие долгосрочные обязательства 2025 42 359 42 359 140 140 26 123 26 120 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>67</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>проценты к уплате</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ProKUpl_1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 11 другие краткосрочные обязательства 2024 1 13 997 2 428 3 484 66 669</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>56</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M25_000000_t23FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>прочие доходы</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ProDoh</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>прочие доходы</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ProDoh_1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>76</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>прочие доходы</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ProDoh_2</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>77</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>проценты к уплате</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ProKUpl_2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>продолжение таблицы 12 доля имущества производственного назначения в валюте баланса 2025 28 4 1 6 71 1 44 6 22 5 57 4</t>
         </is>
       </c>
     </row>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,26 +868,26 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: количество организаций (единиц)</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProKolOrg(ed</t>
+          <t>TeRosPri(ubV%_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -896,13 +896,13 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>темп роста прибыли в</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -911,104 +911,104 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: в % к общему количеству организаций</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProV%KObsKolOrg</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>организации получившие прибыль в к общему количеству</t>
+          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>PriUby(-DoNalZaPreGo_2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов к себестоимости продаж с учетом коммерческ</t>
+          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
+          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo</t>
+          <t>RenUby(-V%KSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_1</t>
+          <t>PriUby(-DoNalZaPreGo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1038,11 +1038,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_2</t>
+          <t>PriUby(-DoNalZaPreGo_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1140,21 +1140,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: убыточность в % :</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProUbyV%:</t>
+          <t>SumUbyZaPreGo_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1164,89 +1164,89 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>организации получившие прибыль в к общему количеству</t>
+          <t>сумма убытка за соответствующий период предыдущего года</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: убыток от продажи</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProUbyOtPro</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>продолжение таблицы 16 организации получившие убыток убыток 3 480</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1276,11 +1276,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1344,11 +1344,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1378,89 +1378,89 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
+          <t>SumPriZaPreGo_2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>сумма убытка за соответствующий период предыдущего года</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
+          <t>RenUby(-V%KSebProSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
+          <t>TeRosPri(ubV%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1470,123 +1470,119 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>уровень рентабельности убыточности в к себестоимости продаж с учетом коммерческих и управленческих расходов к себестоимости продаж с учетом коммерческ</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RenUby(-V%KSebProSUchKomIUprRas_1</t>
+          <t>TeRosPri(ubV%_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M25_000000_t01Ved14mo8.xlsx</t>
+          <t>M25_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>долгосрочные обязательства</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DolOby_1</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>внеоборотные активы 2024</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RenUby(-V%ChiPri(ubKVyr_1</t>
+          <t>SumPriZaPreGo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>продолжение таблицы 21 чистая прибыль убыток в ко всем активам чистая прибыль убыток в ко всем активам 3 8 5 1 8 8 6 8 10 0</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1595,22 +1591,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%</t>
+          <t>TeRosUbyV%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1620,7 +1616,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1629,56 +1625,56 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_1</t>
+          <t>SumPriZaPreGo_1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_2</t>
+          <t>TeRosUbyV%_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1688,55 +1684,55 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M25_000000_t13Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>SumUbyZaPreGo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>M25_000000_t01Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>краткосрочные обязательства</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KraOby_1</t>
+          <t>SumUbyZaPreGo_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1744,1053 +1740,455 @@
           <t>13</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>внеоборотные активы 2024</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>соотношение собственных и заемных средств</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SooSobIZaeSre</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>продолжение таблицы 9 обязательства без заемных средств 2025 61 291 796 15 128 217 45 150 92 736 37 600 55 136</t>
+          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>доля источников финансирования (источники собственных средств и долгосрочные обязательства) в валюте баланса</t>
+          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DolIstFin(isSobSreIDolObyVValBal</t>
+          <t>RenUby(-V%ChiPri(ubKVyr_1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>соотношение заемных и собственных средств нормальное ограничение меньше либо равно 100 2024 соотношение заемных и собственных средств нормальное огран</t>
+          <t>прибыль убыток от продаж прибыль убыток от продаж прибыль убыток от продаж организации получившие убыток от продаж в к общему количеству организаций в</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>M25_000000_t01Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg</t>
+          <t>ProRas</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2024</t>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M25_000000_t01Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
+          <t>ProRas_1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2024</t>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo</t>
+          <t>TeRosSumPriV%_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TeRosUbyV%</t>
+          <t>ProDoh</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов 289</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_1</t>
+          <t>ProRas_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TeRosUbyV%_1</t>
+          <t>ProKUpl</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_2</t>
+          <t>ProKUpl_1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TeRosUbyV%_2</t>
+          <t>ProDoh_1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>139</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>M25_000000_t01Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>рентабельность, убыточность (-) в % к выручке</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal</t>
+          <t>RenUby(-V%KVyr_1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2024</t>
+          <t>прибыль убыток от продаж прибыль убыток от продаж прибыль убыток от продаж организации получившие убыток от продаж в к общему количеству организаций в</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>M25_000000_t01Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
+          <t>ProDoh_2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2024</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % к выручке</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RenUby(-V%KVyr_1</t>
+          <t>ProKUpl_2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам 4 8 4 0 14 5 16 1 13 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>M25_000000_t22Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>коэффициент текущей ликвидности (покрытия) (нормальное ограничение 200 %)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>KoeTekLik(po(noOgr20%)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>соотношение заемных и собственных средств нормальное ограничение меньше либо равно 100 2024 соотношение заемных и собственных средств нормальное огран</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>89</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>сумма убытка за предыдущий год</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SumUbyZaPreGo</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>организации получившие убыток количество организаций единиц</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>104</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>сумма убытка за предыдущий год</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SumUbyZaPreGo_1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>организации получившие убыток количество организаций единиц</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>119</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>сумма убытка за предыдущий год</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SumUbyZaPreGo_2</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>организации получившие убыток количество организаций единиц</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>93</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>108</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%_1</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>123</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%_2</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>13</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>M25_000000_t01Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>капитал и резервы</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>KapIRez_1</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>валюта баланса 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>58</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>прочие расходы</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ProRas</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
           <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>68</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>прочие расходы</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>ProRas_1</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>78</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>прочие расходы</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ProRas_2</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ProKUpl</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 10 другие долгосрочные обязательства 2025 42 359 42 359 140 140 26 123 26 120 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>67</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>ProKUpl_1</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 11 другие краткосрочные обязательства 2024 1 13 997 2 428 3 484 66 669</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>56</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>ProDoh</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>ProDoh_1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>76</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>ProDoh_2</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>77</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>ProKUpl_2</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 12 доля имущества производственного назначения в валюте баланса 2025 28 4 1 6 71 1 44 6 22 5 57 4</t>
         </is>
       </c>
     </row>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -1752,26 +1752,26 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%</t>
+          <t>ProRas</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1780,32 +1780,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RenUby(-V%ChiPri(ubKVyr_1</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -1814,41 +1814,41 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>прибыль убыток от продаж прибыль убыток от продаж прибыль убыток от продаж организации получившие убыток от продаж в к общему количеству организаций в</t>
+          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ProRas</t>
+          <t>RenUby(-V%ChiPri(ubKVyr_1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности выручка</t>
+          <t>прибыль убыток от продаж прибыль убыток от продаж прибыль убыток от продаж организации получившие убыток от продаж в к общему количеству организаций в</t>
         </is>
       </c>
     </row>
@@ -1946,11 +1946,11 @@
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов 289</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,75 +800,75 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M25_000000_t27Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>чистая прибыль, убыток (-) до налогообложения в % к: всем активам</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ChiPriUby(-DoNalV%K:VsAkt</t>
+          <t>TeRosPri(ubV%_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>темп роста прибыли в</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M25_000000_t27Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>чистая прибыль, убыток (-) до налогообложения в % к: всем активам</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ChiPriUby(-DoNalV%K:VsAkt_1</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения в к всем активам</t>
+          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -877,70 +877,70 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_2</t>
+          <t>PriUby(-DoNalZaPreGo_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>темп роста прибыли в</t>
+          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
+          <t>PriUby(-DoNalZaPreGo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_2</t>
+          <t>PriUby(-DoNalZaPreGo_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -960,541 +960,541 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RenUby(-V%KSebProSUchKomIUprRas</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % к выручке</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RenUby(-V%KVyr</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RenUby(-V%ChiPri(ubKVyr</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в чистой прибыли убытка к выручке чистой прибыли убытка к выручке</t>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_2</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>сумма убытка за соответствующий период предыдущего года</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
+          <t>TeRosPri(ubV%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
+          <t>TeRosPri(ubV%_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>0.61</v>
+        <v>0.4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>TeRosUbyV%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
+          <t>SumPriZaPreGo_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
+          <t>TeRosUbyV%_1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0.58</v>
+        <v>0.35</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>сумма убытка за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_2</t>
+          <t>SumUbyZaPreGo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>сумма убытка за соответствующий период предыдущего года</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>сумма прибыли за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RenUby(-V%KSebProSUchKomIUprRas_1</t>
+          <t>SumPriZaPreGo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%</t>
+          <t>SumUbyZaPreGo_1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_1</t>
+          <t>ProRas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1504,109 +1504,109 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M25_000000_t13Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo</t>
+          <t>ProRas_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TeRosUbyV%</t>
+          <t>TeRosSumPriV%_1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1616,577 +1616,237 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_1</t>
+          <t>ProDoh</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TeRosUbyV%_1</t>
+          <t>ProRas_2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo</t>
+          <t>ProKUpl</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_1</t>
+          <t>ProKUpl_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ProRas</t>
+          <t>ProDoh_1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%</t>
+          <t>ProDoh_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>рентабельность, убыточность (-) в % чистой прибыли (убытка) к выручке</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RenUby(-V%ChiPri(ubKVyr_1</t>
+          <t>ProKUpl_2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="H42" t="inlineStr">
-        <is>
-          <t>прибыль убыток от продаж прибыль убыток от продаж прибыль убыток от продаж организации получившие убыток от продаж в к общему количеству организаций в</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>68</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>прочие расходы</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ProRas_1</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>доходы и расходы по обычным видам деятельности выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>108</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%_1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>56</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ProDoh</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>78</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>прочие расходы</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>ProRas_2</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>57</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ProKUpl</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>67</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ProKUpl_1</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>66</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>ProDoh_1</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>139</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>рентабельность, убыточность (-) в % к выручке</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RenUby(-V%KVyr_1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>прибыль убыток от продаж прибыль убыток от продаж прибыль убыток от продаж организации получившие убыток от продаж в к общему количеству организаций в</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>76</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ProDoh_2</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>77</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ProKUpl_2</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H52" t="inlineStr">
         <is>
           <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,21 +800,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_2</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -824,55 +824,55 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>темп роста прибыли в</t>
+          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
+          <t>PriUby(-DoNalZaPreGo_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_2</t>
+          <t>PriUby(-DoNalZaPreGo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -892,21 +892,21 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo</t>
+          <t>PriUby(-DoNalZaPreGo_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -936,45 +936,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_1</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1004,45 +1004,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1072,113 +1072,113 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
+          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
+          <t>TeRosPri(ubV%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%</t>
+          <t>TeRosPri(ubV%_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1208,94 +1208,94 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_1</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M25_000000_t13Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>TeRosUbyV%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TeRosUbyV%</t>
+          <t>SumPriZaPreGo_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1304,13 +1304,13 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_1</t>
+          <t>TeRosUbyV%_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>сумма убытка за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TeRosUbyV%_1</t>
+          <t>SumUbyZaPreGo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1387,51 +1387,51 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>сумма убытка за соответствующий период предыдущего года</t>
+          <t>сумма прибыли за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo</t>
+          <t>SumPriZaPreGo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>сумма прибыли за соответствующий период предыдущего года</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo</t>
+          <t>SumUbyZaPreGo_1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1440,66 +1440,66 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_1</t>
+          <t>ProRas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ProRas</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -1508,66 +1508,66 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%</t>
+          <t>ProRas_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ProRas_1</t>
+          <t>TeRosSumPriV%_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1576,119 +1576,119 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности выручка</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%_1</t>
+          <t>ProDoh</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>прочие доходы</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ProDoh</t>
+          <t>ProRas_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ProRas_2</t>
+          <t>ProKUpl</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ProKUpl</t>
+          <t>ProKUpl_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1712,13 +1712,13 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1727,36 +1727,36 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>проценты к уплате</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ProKUpl_1</t>
+          <t>ProDoh_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ProDoh_1</t>
+          <t>ProDoh_2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1795,58 +1795,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>прочие доходы</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ProDoh_2</t>
+          <t>ProKUpl_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="H41" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>77</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ProKUpl_2</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H42" t="inlineStr">
         <is>
           <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,157 +936,157 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>TeRosPri(ubV%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
+          <t>TeRosPri(ubV%_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1096,51 +1096,51 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DohIRasPoObyVidDeySebSUchKomIUprRas_2</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности прибыль убыток от продаж прибыль убыток от продаж</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%</t>
+          <t>TeRosUbyV%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1183,66 +1183,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_1</t>
+          <t>SumPriZaPreGo_1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M25_000000_t13Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>TeRosUbyV%_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1251,46 +1251,46 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>сумма убытка за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TeRosUbyV%</t>
+          <t>SumUbyZaPreGo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>сумма прибыли за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_1</t>
+          <t>SumPriZaPreGo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1319,66 +1319,66 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TeRosUbyV%_1</t>
+          <t>SumUbyZaPreGo_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>сумма убытка за соответствующий период предыдущего года</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo</t>
+          <t>ProRas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1387,138 +1387,138 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>сумма прибыли за соответствующий период предыдущего года</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
+          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_1</t>
+          <t>ProRas_1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ProRas</t>
+          <t>TeRosSumPriV%_1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%</t>
+          <t>ProDoh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ProRas_1</t>
+          <t>ProRas_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1538,157 +1538,157 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности выручка</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%_1</t>
+          <t>ProKUpl</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>прочие доходы</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ProDoh</t>
+          <t>ProKUpl_1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ProRas_2</t>
+          <t>ProDoh_1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>проценты к уплате</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ProKUpl</t>
+          <t>ProDoh_2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ProKUpl_1</t>
+          <t>ProKUpl_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1708,111 +1708,9 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H38" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>66</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ProDoh_1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>76</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>прочие доходы</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ProDoh_2</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>77</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>проценты к уплате</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ProKUpl_2</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H41" t="inlineStr">
         <is>
           <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,147 +630,147 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PreGo(soKruDohIRasPoObyVidDeySebSUchKomIUprRas</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 доходы и расходы по обычным видам деятельности себестоимость с учетом коммерческих и управленческих расходов</t>
+          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности прибыль, убыток (-) от продаж</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PreGo(soKruDohIRasPoObyVidDeyPriUby(-OtPro</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 доходы и расходы по обычным видам деятельности прибыль убыток от продаж</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S25_000000_t26Ved14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) доходы и расходы по обычным видам деятельности выручка</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PreGo(soKruDohIRasPoObyVidDeyVyr</t>
+          <t>KolOrgPolUbyZaPreGo(ed_2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 доходы и расходы по обычным видам деятельности выручка</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed</t>
+          <t>KolOrgPolUbyZaPreGo(ed_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -800,143 +800,143 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>Pri(ubOtProDeyDoNalZaPreGo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_2</t>
+          <t>Pri(ubOtProDeyDoNalZaPreGo_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_3</t>
+          <t>Pri(ubOtProDeyDoNalZaPreGo_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) сальдо прочих доходов и расходов</t>
+          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PreGo(soKruSalProDohIRas</t>
+          <t>Pri(ubOtProDeyDoNalZaPreGo_3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -945,32 +945,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pri(ubOtProDeyDoNalZaPreGo</t>
+          <t>TeRosPri(ubV%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -979,32 +979,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pri(ubOtProDeyDoNalZaPreGo_1</t>
+          <t>TeRosPri(ubV%_1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1013,32 +1013,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pri(ubOtProDeyDoNalZaPreGo_2</t>
+          <t>TeRosPri(ubV%_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1047,46 +1047,46 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>прибыль (убыток) от продолжающейся деятельности до налогообложения за предыдущий год</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pri(ubOtProDeyDoNalZaPreGo_3</t>
+          <t>TeRosPri(ubV%_3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) прибыль (убыток) от продолжающейся деятельности до налогообложения</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PreGo(soKruPri(ubOtProDeyDoNal</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1115,22 +1115,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста суммы убытка в %</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%</t>
+          <t>TeRosSumUbyV%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста суммы убытка в %</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_1</t>
+          <t>TeRosSumUbyV%_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1183,22 +1183,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста суммы убытка в %</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_2</t>
+          <t>TeRosSumUbyV%_2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>темп роста суммы убытка в %</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_3</t>
+          <t>TeRosSumUbyV%_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1242,191 +1242,191 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t01Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) чистая прибыль (убыток)</t>
+          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PreGo(soKruChiPri(ub</t>
+          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 чистая прибыль убыток отчетного периода чистая прибыль убыток отчетного периода</t>
+          <t>на конец года тысяч рублей оборотные активы 2024</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S25_000000_t13Ved14.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>SumPriZaPreGo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>темп роста суммы убытка в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TeRosSumUbyV%</t>
+          <t>SumPriZaPreGo_1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>темп роста суммы убытка в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TeRosSumUbyV%_1</t>
+          <t>SumPriZaPreGo_2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
+          <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>темп роста суммы убытка в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TeRosSumUbyV%_2</t>
+          <t>SumPriZaPreGo_3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
+          <t>S25_000000_t01Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>темп роста суммы убытка в %</t>
+          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TeRosSumUbyV%_3</t>
+          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1436,51 +1436,51 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>на конец года тысяч рублей оборотные активы 2024</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S25_000000_t01Ved14mo8.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года итог актива убыточных организаций</t>
+          <t>предыдущий год (сопоставимый круг) проценты к уплате</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoItAktUbyOrg_1</t>
+          <t>PreGo(soKruProKUpl</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2024</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1489,32 +1489,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo</t>
+          <t>SumUbyZaPreGo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1523,32 +1523,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_1</t>
+          <t>SumUbyZaPreGo_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_2</t>
+          <t>SumUbyZaPreGo_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1591,466 +1591,228 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_3</t>
+          <t>SumUbyZaPreGo_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S25_000000_t01Ved14mo8.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>валюта баланса убыточных организаций, на конец года в % к валюте баланса</t>
+          <t>предыдущий год (сопоставимый круг) прочие расходы</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ValBalUbyOrgNaKonGoV%KValBal_1</t>
+          <t>PreGo(soKruProRas</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей оборотные активы 2024</t>
+          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) проценты к уплате</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PreGo(soKruProKUpl</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>предыдущий год (сопоставимый круг) налог на прибыль</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PreGo(soKruNalNaPri</t>
+          <t>TeRosSumPriV%_1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo</t>
+          <t>TeRosSumPriV%_2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
+          <t>S25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_1</t>
+          <t>TeRosSumPriV%_3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>предыдущий год (сопоставимый круг) прочие доходы</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_2</t>
+          <t>PreGo(soKruProDoh</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H41" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>126</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>сумма убытка за предыдущий год</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SumUbyZaPreGo_3</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток количество организаций единиц</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>70</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>предыдущий год (сопоставимый круг) прочие расходы</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PreGo(soKruProRas</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>85</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>100</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%_1</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>115</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%_2</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>130</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>темп роста суммы прибыли в %</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TeRosSumPriV%_3</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>68</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>S25_000000_t23-прVed14.xlsx</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>предыдущий год (сопоставимый круг) прочие доходы</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>PreGo(soKruProDoh</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H48" t="inlineStr">
         <is>
           <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>

--- a/output/неиспользованные_показатели.xlsx
+++ b/output/неиспользованные_показатели.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,79 +800,83 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t22Ved14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>коэффициент обеспеченности собственными материальными оборотными средствами</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
+          <t>KoeObeSobMatOboSre</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
+          <t>коэффициент обеспеченности собственными оборотными средствами 2024</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t26Ved14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_2</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
+          <t>продолжение таблицы 19 организации получившие убыток от продаж убыточность в к себестоимости продаж с учетом коммерческих и управленческих расходов</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -882,7 +886,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo</t>
+          <t>PriUby(-DoNalZaPreGo_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -892,21 +896,21 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>прибыль убыток до налогообложения за аналогичный период предыдущего года</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,7 +920,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PriUby(-DoNalZaPreGo_1</t>
+          <t>PriUby(-DoNalZaPreGo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -936,45 +940,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
+          <t>прибыль, убыток (-) до налогообложения за предыдущий год</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed</t>
+          <t>PriUby(-DoNalZaPreGo_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>количество организаций единиц количество организаций единиц</t>
+          <t>прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KolOrgPolUbyZaPreGo(ed_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1004,55 +1008,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M25_000000_t26Ved14mo8.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
+          <t>количество организаций, получивших убыток за предыдуший год (единиц)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
+          <t>KolOrgPolUbyZaPreGo(ed_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
+          <t>количество организаций единиц количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>темп роста прибыли (убытка) в %</t>
+          <t>организации, получившие убыток от продаж: себестоимость продаж с учетом коммерческих и управлеческих расходов</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%</t>
+          <t>OrgPolUbyOtProSebProSUchKomIUprRas_1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1062,21 +1066,21 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>тысяч рублей уровень рентабельности убыточности в к выручке к выручке продолжение таблицы 20 организации получившие убыток от продаж убыточность в к с</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TeRosPri(ubV%_1</t>
+          <t>TeRosPri(ubV%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1106,94 +1110,94 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M25_000000_t13Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>средняя стоимость оборотных активов, тыс.рублей</t>
+          <t>темп роста прибыли (убытка) в %</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SreStoOboAktTys</t>
+          <t>TeRosPri(ubV%_1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>оборотные активы длительность 1 оборота</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t13Ved14.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>средняя стоимость оборотных активов, тыс.рублей</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TeRosUbyV%</t>
+          <t>SreStoOboAktTys</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>оборотные активы длительность 1 оборота</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>сумма прибыли за предыдущий год</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo_1</t>
+          <t>TeRosUbyV%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1202,13 +1206,13 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>организации получившие прибыль количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1217,17 +1221,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>темп роста убытка в %</t>
+          <t>сумма прибыли за предыдущий год</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TeRosUbyV%_1</t>
+          <t>SumPriZaPreGo_1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1236,47 +1240,47 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>организации получившие прибыль количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>сумма убытка за соответствующий период предыдущего года</t>
+          <t>темп роста убытка в %</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo</t>
+          <t>TeRosUbyV%_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1285,51 +1289,51 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>сумма прибыли за соответствующий период предыдущего года</t>
+          <t>сумма убытка за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SumPriZaPreGo</t>
+          <t>SumUbyZaPreGo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>сумма убытка за предыдущий год</t>
+          <t>сумма прибыли за соответствующий период предыдущего года</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SumUbyZaPreGo_1</t>
+          <t>SumPriZaPreGo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1338,66 +1342,66 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>организации получившие убыток количество организаций единиц</t>
+          <t>организации получившие прибыль в к общему количеству организации получившие прибыль в к общему количеству</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>сумма убытка за предыдущий год</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ProRas</t>
+          <t>SumUbyZaPreGo_1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>организации получившие убыток количество организаций единиц</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M25_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%</t>
+          <t>ProRas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1406,66 +1410,66 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ProRas_1</t>
+          <t>TeRosSumPriV%</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>доходы и расходы по обычным видам деятельности выручка</t>
+          <t>продолжение таблицы 16 организации получившие прибыль прибыль до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>темп роста суммы прибыли в %</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TeRosSumPriV%_1</t>
+          <t>ProRas_1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1474,119 +1478,119 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>тысяч рублей организации получившие убыток убыток</t>
+          <t>доходы и расходы по обычным видам деятельности выручка</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t25FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>прочие доходы</t>
+          <t>темп роста суммы прибыли в %</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ProDoh</t>
+          <t>TeRosSumPriV%_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>тысяч рублей организации получившие убыток убыток</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>прочие расходы</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ProRas_2</t>
+          <t>ProDoh</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+          <t>сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>проценты к уплате</t>
+          <t>прочие расходы</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ProKUpl</t>
+          <t>ProRas_2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M25_000000_t23OpfVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1596,7 +1600,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ProKUpl_1</t>
+          <t>ProKUpl</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1610,13 +1614,13 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
+          <t>продолжение таблицы 13 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1625,36 +1629,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>прочие доходы</t>
+          <t>проценты к уплате</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ProDoh_1</t>
+          <t>ProKUpl_1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
+          <t>продолжение таблицы 14 прибыль убыток до налогообложения прибыль убыток до налогообложения</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M25_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1664,7 +1668,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ProDoh_2</t>
+          <t>ProDoh_1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1674,17 +1678,17 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+          <t>продолжение таблицы 14 сальдо прочих доходов и расходов сальдо прочих доходов и расходов</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1693,24 +1697,58 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>проценты к уплате</t>
+          <t>прочие доходы</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ProKUpl_2</t>
+          <t>ProDoh_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>77</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>проценты к уплате</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ProKUpl_2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0.17</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>тысяч рублей доходы и расходы по обычным видам деятельности выручка выручка</t>
         </is>
